--- a/templates/산출근거_표준.xlsx
+++ b/templates/산출근거_표준.xlsx
@@ -463,8 +463,11 @@
         <v>현금 (N)</v>
       </c>
       <c r="F4" s="1" t="e">
-        <f>'1차년도_250520'!G13</f>
-      </c>
+        <f>산출근거!G13</f>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="1" t="e">
         <f>SUM(F4:I4)</f>
       </c>
@@ -477,8 +480,11 @@
         <v>현물</v>
       </c>
       <c r="F5" s="1" t="e">
-        <f>'1차년도_250520'!G14</f>
-      </c>
+        <f>산출근거!G14</f>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="1" t="e">
         <f>SUM(F5:I5)</f>
       </c>
@@ -493,8 +499,11 @@
         <v>현금 (O)</v>
       </c>
       <c r="F6" s="1" t="e">
-        <f>'1차년도_250520'!G15</f>
-      </c>
+        <f>산출근거!G15</f>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
       <c r="J6" s="1" t="e">
         <f>SUM(F6:I6)</f>
       </c>
@@ -507,8 +516,11 @@
         <v>현물</v>
       </c>
       <c r="F7" s="1" t="e">
-        <f>'1차년도_250520'!G16</f>
-      </c>
+        <f>산출근거!G16</f>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
       <c r="J7" s="1" t="e">
         <f>SUM(F7:I7)</f>
       </c>
@@ -523,8 +535,11 @@
         <v>현금 (P)</v>
       </c>
       <c r="F8" s="1" t="e">
-        <f>'1차년도_250520'!G17</f>
-      </c>
+        <f>산출근거!G17</f>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="e">
         <f>SUM(F8:I8)</f>
       </c>
@@ -537,8 +552,11 @@
         <v>현물</v>
       </c>
       <c r="F9" s="1" t="e">
-        <f>'1차년도_250520'!G18</f>
-      </c>
+        <f>산출근거!G18</f>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="1" t="e">
         <f>SUM(F9:I9)</f>
       </c>
@@ -551,8 +569,11 @@
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" s="1" t="e">
-        <f>'1차년도_250520'!G19</f>
-      </c>
+        <f>산출근거!G19</f>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="1" t="e">
         <f>SUM(F10:I10)</f>
       </c>
@@ -563,8 +584,11 @@
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11" s="1" t="e">
-        <f>'1차년도_250520'!G20</f>
-      </c>
+        <f>산출근거!G20</f>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
       <c r="J11" s="1" t="e">
         <f>SUM(F11:I11)</f>
       </c>
@@ -577,8 +601,11 @@
       <c r="D12"/>
       <c r="E12"/>
       <c r="F12" s="1" t="e">
-        <f>'1차년도_250520'!G21</f>
-      </c>
+        <f>산출근거!G21</f>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="1" t="e">
         <f>SUM(F12:I12)</f>
       </c>
@@ -591,8 +618,11 @@
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13" s="1" t="e">
-        <f>'1차년도_250520'!G22</f>
-      </c>
+        <f>산출근거!G22</f>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
       <c r="J13" s="1" t="e">
         <f>SUM(F13:I13)</f>
       </c>
@@ -607,8 +637,11 @@
         <v>현금 (R)</v>
       </c>
       <c r="F14" s="1" t="e">
-        <f>'1차년도_250520'!G23</f>
-      </c>
+        <f>산출근거!G23</f>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
       <c r="J14" s="1" t="e">
         <f>SUM(F14:I14)</f>
       </c>
@@ -621,8 +654,11 @@
         <v>현물</v>
       </c>
       <c r="F15" s="1" t="e">
-        <f>'1차년도_250520'!G24</f>
-      </c>
+        <f>산출근거!G24</f>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
       <c r="J15" s="1" t="e">
         <f>SUM(F15:I15)</f>
       </c>
@@ -635,8 +671,11 @@
       <c r="D16"/>
       <c r="E16"/>
       <c r="F16" s="1" t="e">
-        <f>'1차년도_250520'!G25</f>
-      </c>
+        <f>산출근거!G25</f>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
       <c r="J16" s="1" t="e">
         <f>SUM(F16:I16)</f>
       </c>
@@ -651,8 +690,11 @@
         <v>현금 (S)</v>
       </c>
       <c r="F17" s="1" t="e">
-        <f>'1차년도_250520'!G26</f>
-      </c>
+        <f>산출근거!G26</f>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
       <c r="J17" s="1" t="e">
         <f>SUM(F17:I17)</f>
       </c>
@@ -665,8 +707,11 @@
         <v>현물</v>
       </c>
       <c r="F18" s="1" t="e">
-        <f>'1차년도_250520'!G27</f>
-      </c>
+        <f>산출근거!G27</f>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
       <c r="J18" s="1" t="e">
         <f>SUM(F18:I18)</f>
       </c>
@@ -681,8 +726,11 @@
         <v>현금 (T)</v>
       </c>
       <c r="F19" s="1" t="e">
-        <f>'1차년도_250520'!G28</f>
-      </c>
+        <f>산출근거!G28</f>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="1" t="e">
         <f>SUM(F19:I19)</f>
       </c>
@@ -695,8 +743,11 @@
         <v>현물</v>
       </c>
       <c r="F20" s="1" t="e">
-        <f>'1차년도_250520'!G29</f>
-      </c>
+        <f>산출근거!G29</f>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
       <c r="J20" s="1" t="e">
         <f>SUM(F20:I20)</f>
       </c>
@@ -711,8 +762,11 @@
         <v>현금 (U)</v>
       </c>
       <c r="F21" s="1" t="e">
-        <f>'1차년도_250520'!G30</f>
-      </c>
+        <f>산출근거!G30</f>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
       <c r="J21" s="1" t="e">
         <f>SUM(F21:I21)</f>
       </c>
@@ -725,8 +779,11 @@
         <v>현물</v>
       </c>
       <c r="F22" s="1" t="e">
-        <f>'1차년도_250520'!G31</f>
-      </c>
+        <f>산출근거!G31</f>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="1" t="e">
         <f>SUM(F22:I22)</f>
       </c>
@@ -738,9 +795,12 @@
       </c>
       <c r="D23"/>
       <c r="E23"/>
-      <c r="F23" s="1" t="e">
-        <f>'1차년도_250520'!G32</f>
-      </c>
+      <c r="F23" s="2" t="e">
+        <f>산출근거!G32</f>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
       <c r="J23" s="2" t="e">
         <f>SUM(F23:I23)</f>
       </c>
@@ -755,8 +815,11 @@
         <v>현금 (J)</v>
       </c>
       <c r="F24" s="1" t="e">
-        <f>'1차년도_250520'!G33</f>
-      </c>
+        <f>산출근거!G33</f>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="1" t="e">
         <f>SUM(F24:I24)</f>
       </c>
@@ -769,8 +832,11 @@
         <v>현물</v>
       </c>
       <c r="F25" s="1" t="e">
-        <f>'1차년도_250520'!G34</f>
-      </c>
+        <f>산출근거!G34</f>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
       <c r="J25" s="1" t="e">
         <f>SUM(F25:I25)</f>
       </c>
@@ -781,8 +847,11 @@
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" s="1" t="e">
-        <f>'1차년도_250520'!G35</f>
-      </c>
+        <f>산출근거!G35</f>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
       <c r="J26" s="1" t="e">
         <f>SUM(F26:I26)</f>
       </c>
@@ -795,8 +864,11 @@
       <c r="D27"/>
       <c r="E27"/>
       <c r="F27" s="1" t="e">
-        <f>'1차년도_250520'!G36</f>
-      </c>
+        <f>산출근거!G36</f>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
       <c r="J27" s="1" t="e">
         <f>SUM(F27:I27)</f>
       </c>
@@ -809,8 +881,11 @@
       <c r="D28"/>
       <c r="E28"/>
       <c r="F28" s="3" t="e">
-        <f>'1차년도_250520'!G37</f>
-      </c>
+        <f>산출근거!G37</f>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
       <c r="J28" s="3" t="e">
         <f>SUM(F28:I28)</f>
       </c>
@@ -823,8 +898,11 @@
       <c r="D29"/>
       <c r="E29"/>
       <c r="F29" s="1" t="e">
-        <f>'1차년도_250520'!G38</f>
-      </c>
+        <f>산출근거!G38</f>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
       <c r="J29" s="1" t="e">
         <f>SUM(F29:I29)</f>
       </c>
@@ -837,8 +915,11 @@
       <c r="D30"/>
       <c r="E30"/>
       <c r="F30" s="1" t="e">
-        <f>'1차년도_250520'!G39</f>
-      </c>
+        <f>산출근거!G39</f>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="e">
         <f>SUM(F30:I30)</f>
       </c>
@@ -2376,7 +2457,9 @@
       <c r="N64"/>
     </row>
     <row r="65">
-      <c r="C65"/>
+      <c r="C65" t="str">
+        <v>기존인력</v>
+      </c>
       <c r="D65"/>
       <c r="E65"/>
       <c r="F65" s="1"/>
@@ -2470,7 +2553,7 @@
       <c r="I69" s="8"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="e">
-        <f>TRUNC(G69*H69*I69,-3)-270000</f>
+        <f>TRUNC(G69*H69*I69,-3)</f>
       </c>
       <c r="L69" s="1" t="e">
         <f>SUM(J69:K69)</f>
@@ -2532,7 +2615,7 @@
       <c r="H72" s="7"/>
       <c r="I72" s="8"/>
       <c r="J72" s="1" t="e">
-        <f>TRUNC(G72*H72*I72,-3)-30000</f>
+        <f>TRUNC(G72*H72*I72,-3)</f>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1" t="e">
@@ -2574,7 +2657,7 @@
       <c r="H74" s="7"/>
       <c r="I74" s="8"/>
       <c r="J74" s="1" t="e">
-        <f>TRUNC(G74*H74*I74,-3)-7000</f>
+        <f>TRUNC(G74*H74*I74,-3)</f>
       </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1" t="e">
@@ -2616,7 +2699,7 @@
       <c r="H76" s="7"/>
       <c r="I76" s="8"/>
       <c r="J76" s="1" t="e">
-        <f>TRUNC(G76*H76*I76,-3)-6000</f>
+        <f>TRUNC(G76*H76*I76,-3)</f>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="e">
@@ -2658,7 +2741,7 @@
       <c r="H78" s="7"/>
       <c r="I78" s="8"/>
       <c r="J78" s="1" t="e">
-        <f>TRUNC(G78*H78*I78,-3)-5000</f>
+        <f>TRUNC(G78*H78*I78,-3)</f>
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="e">
@@ -2679,7 +2762,7 @@
       <c r="H79" s="7"/>
       <c r="I79" s="8"/>
       <c r="J79" s="1" t="e">
-        <f>TRUNC(G79*H79*I79,-3)-5000</f>
+        <f>TRUNC(G79*H79*I79,-3)</f>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1" t="e">
@@ -2721,7 +2804,7 @@
       <c r="H81" s="7"/>
       <c r="I81" s="8"/>
       <c r="J81" s="1" t="e">
-        <f>TRUNC(G81*H81*I81,-3)-5000</f>
+        <f>TRUNC(G81*H81*I81,-3)</f>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="e">
@@ -2890,7 +2973,9 @@
       <c r="P88" s="1"/>
     </row>
     <row r="89" ht="17.5" customHeight="1">
-      <c r="C89"/>
+      <c r="C89" t="str">
+        <v>신규채용</v>
+      </c>
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89" s="1"/>
@@ -3945,8 +4030,12 @@
       <c r="E160" t="str">
         <v>단가</v>
       </c>
-      <c r="F160"/>
-      <c r="G160"/>
+      <c r="F160" t="str">
+        <v>회</v>
+      </c>
+      <c r="G160" t="str">
+        <v>월</v>
+      </c>
       <c r="H160"/>
       <c r="I160"/>
       <c r="J160"/>
@@ -4050,8 +4139,12 @@
       <c r="E167" t="str">
         <v>단가</v>
       </c>
-      <c r="F167"/>
-      <c r="G167"/>
+      <c r="F167" t="str">
+        <v>회</v>
+      </c>
+      <c r="G167" t="str">
+        <v>월</v>
+      </c>
       <c r="H167"/>
       <c r="I167"/>
       <c r="J167"/>
@@ -4187,7 +4280,9 @@
       <c r="E176" t="str">
         <v>단가</v>
       </c>
-      <c r="F176"/>
+      <c r="F176" t="str">
+        <v>회</v>
+      </c>
       <c r="G176"/>
       <c r="H176"/>
       <c r="I176"/>
@@ -4313,7 +4408,9 @@
       <c r="C184" t="str">
         <v>내역</v>
       </c>
-      <c r="D184"/>
+      <c r="D184" t="str">
+        <v>직급</v>
+      </c>
       <c r="E184" t="str">
         <v>산출내역</v>
       </c>
@@ -4422,7 +4519,9 @@
       <c r="C190" t="str">
         <v>내역</v>
       </c>
-      <c r="D190"/>
+      <c r="D190" t="str">
+        <v>직급</v>
+      </c>
       <c r="E190" t="str">
         <v>산출내역</v>
       </c>
@@ -4536,13 +4635,17 @@
       <c r="F197" t="str">
         <v>시트(수량)</v>
       </c>
-      <c r="G197"/>
+      <c r="G197" t="str">
+        <v>월</v>
+      </c>
       <c r="H197"/>
       <c r="I197"/>
       <c r="J197"/>
       <c r="K197"/>
       <c r="L197"/>
-      <c r="N197"/>
+      <c r="N197" t="str">
+        <v>1년 시트</v>
+      </c>
       <c r="O197"/>
       <c r="P197"/>
     </row>
@@ -4859,8 +4962,12 @@
       <c r="E218" t="str">
         <v>단가</v>
       </c>
-      <c r="F218"/>
-      <c r="G218"/>
+      <c r="F218" t="str">
+        <v>회</v>
+      </c>
+      <c r="G218" t="str">
+        <v>월</v>
+      </c>
       <c r="H218"/>
       <c r="I218"/>
       <c r="J218"/>
@@ -4994,8 +5101,12 @@
       <c r="E227" t="str">
         <v>단가</v>
       </c>
-      <c r="F227"/>
-      <c r="G227"/>
+      <c r="F227" t="str">
+        <v>회</v>
+      </c>
+      <c r="G227" t="str">
+        <v>월</v>
+      </c>
       <c r="H227"/>
       <c r="I227"/>
       <c r="J227"/>
@@ -5108,7 +5219,9 @@
       <c r="E236" t="str">
         <v>단가</v>
       </c>
-      <c r="F236"/>
+      <c r="F236" t="str">
+        <v>회</v>
+      </c>
       <c r="G236"/>
       <c r="H236"/>
       <c r="I236"/>
